--- a/09_Project_Management_Evidence/Project_Schedule_and_Sprint_Backlog.xlsx
+++ b/09_Project_Management_Evidence/Project_Schedule_and_Sprint_Backlog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gedion\Desktop\TrackWIL\09_Project_Management_Evidence\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5391694C-6943-4233-A5B8-E2303543757E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF3E0BD7-F108-4642-BD53-272FD3E7A7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15480" yWindow="660" windowWidth="15600" windowHeight="18720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tracker" sheetId="1" r:id="rId1"/>
@@ -330,24 +330,15 @@
     <t>Not Started</t>
   </si>
   <si>
-    <t>Issue I02 in Risk Register; Defect Log</t>
-  </si>
-  <si>
     <t>T26</t>
   </si>
   <si>
     <t>Execute all test cases with actual results; complete Defect Log and Requirements Traceability Matrix</t>
   </si>
   <si>
-    <t>Dylan Shepard, Sihle Kayise</t>
-  </si>
-  <si>
     <t>In Progress</t>
   </si>
   <si>
-    <t>06_Testing_Results_and_Evaluation workbooks</t>
-  </si>
-  <si>
     <t>T27</t>
   </si>
   <si>
@@ -375,9 +366,6 @@
     <t>Fix defect: entry stays Pending when its link expires; retest</t>
   </si>
   <si>
-    <t>Issue I03 in Risk Register; Defect Log</t>
-  </si>
-  <si>
     <t>T30</t>
   </si>
   <si>
@@ -475,6 +463,18 @@
   </si>
   <si>
     <t>Demo Script</t>
+  </si>
+  <si>
+    <t>Gedion Basson (automated suite); Sihle Kayise (manual TC-001 to TC-014)</t>
+  </si>
+  <si>
+    <t>Test_Cases_and_Results, Defect_Log, Requirements_Traceability_Matrix; tests/system-tests.mjs (36/36 pass)</t>
+  </si>
+  <si>
+    <t>Commit 5268c2e (branch gedion/fix-defects); DEF-01 closed; TC-121 pass</t>
+  </si>
+  <si>
+    <t>Commit 5268c2e; DEF-02 closed; TC-137 pass</t>
   </si>
 </sst>
 </file>
@@ -1733,7 +1733,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>98</v>
       </c>
@@ -1756,27 +1756,27 @@
         <v>15</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="I28" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" s="6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
         <v>101</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
-        <v>102</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>86</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="E29" s="7">
         <v>46318</v>
@@ -1788,24 +1788,24 @@
         <v>15</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>105</v>
+        <v>16</v>
       </c>
       <c r="I29" s="8">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>106</v>
+        <v>147</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>86</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>14</v>
@@ -1826,18 +1826,18 @@
         <v>0</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>86</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>14</v>
@@ -1852,56 +1852,56 @@
         <v>15</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I31" s="8">
         <v>0.5</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="E32" s="7">
         <v>46319</v>
       </c>
       <c r="F32" s="7">
-        <v>46321</v>
+        <v>46318</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="I32" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>116</v>
+        <v>149</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B33" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C33" s="6" t="s">
         <v>114</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>118</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>30</v>
@@ -1922,18 +1922,18 @@
         <v>0</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>39</v>
@@ -1948,24 +1948,24 @@
         <v>43</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="I34" s="8">
         <v>0</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>76</v>
@@ -1980,24 +1980,24 @@
         <v>15</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I35" s="8">
         <v>0.3</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>14</v>
@@ -2018,18 +2018,18 @@
         <v>0</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>14</v>
@@ -2050,18 +2050,18 @@
         <v>0</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>39</v>
@@ -2082,21 +2082,21 @@
         <v>0</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E39" s="7">
         <v>46319</v>
@@ -2114,21 +2114,21 @@
         <v>0</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E40" s="7">
         <v>46319</v>
@@ -2146,18 +2146,18 @@
         <v>0</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>14</v>
@@ -2178,21 +2178,21 @@
         <v>0</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E42" s="7">
         <v>46323</v>
@@ -2210,7 +2210,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
